--- a/scouting_merged.xlsx
+++ b/scouting_merged.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -484,15 +484,16 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -533,45 +534,50 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Teleop Fuel</t>
+          <t>Balls/Sec</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Field Zone</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Endgame Climb</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Defense Rating</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Driver Rating</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Played Defense</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>_source</t>
         </is>
@@ -586,7 +592,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -595,7 +601,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -606,53 +612,56 @@
         <v/>
       </c>
       <c r="H2" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Trench</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v/>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>broken intake</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31T01:50:59.364Z</t>
+          <t>dual shooter</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-03-31 (1).csv</t>
+          <t>2026-04-01T19:11:10.947Z</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-01.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8767</v>
+        <v>5460</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -661,7 +670,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -672,108 +681,43 @@
         <v/>
       </c>
       <c r="H3" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Trench</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
         <v/>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>strong shooter</t>
-        </is>
-      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31T02:14:04.557Z</t>
+          <t>drum shooter</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-03-31 (1).csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>8767</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Joe</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5 pt pen</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-31T01:57:22.179Z</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>scouting_2026-03-31 (1).csv</t>
+          <t>2026-04-01T19:11:43.244Z</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-01.csv</t>
         </is>
       </c>
     </row>
@@ -788,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -797,13 +741,14 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -839,35 +784,40 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Teleop Fuel</t>
+          <t>Balls/Sec</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>Field Zone</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Endgame Climb</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Defense Rating</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Driver Rating</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Played Defense</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -875,18 +825,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8767</v>
+        <v>5460</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -897,30 +847,33 @@
         <v/>
       </c>
       <c r="G2" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Trench</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
         <v/>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="K2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>broken intake</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>drum shooter</t>
         </is>
       </c>
     </row>
@@ -933,11 +886,11 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -948,83 +901,33 @@
         <v/>
       </c>
       <c r="G3" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Trench</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v/>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>strong shooter</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>8767</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5 pt pen</t>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>dual shooter</t>
         </is>
       </c>
     </row>
@@ -1039,13 +942,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1070,12 +973,12 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Avg Teleop Fuel</t>
+          <t>Avg Balls/Sec</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Avg Total Fuel</t>
+          <t>Avg Accuracy %</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
@@ -1096,28 +999,54 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
+        <v>5460</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>8767</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>4.67</v>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/scouting_merged.xlsx
+++ b/scouting_merged.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -726,7 +726,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9756</v>
+        <v>7658</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -735,67 +735,65 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v/>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
         <v/>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v/>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Fast lil guy</t>
+          <t>Stuck field fault</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:08:14.410Z</t>
+          <t>2026-04-10T15:05:27.833Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10.csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9208</v>
+        <v>9756</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -808,7 +806,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -819,21 +817,21 @@
         <v/>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Trench</t>
+          <t>Bump</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
         <v/>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>4</v>
@@ -845,12 +843,12 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Auto geeked out very fast intake didn't shoot any balls something must've been wrong</t>
+          <t>Fast lil guy</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T15:17:50.246Z</t>
+          <t>2026-04-10T15:08:14.410Z</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -864,7 +862,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10642</v>
+        <v>3234</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -873,7 +871,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -881,17 +879,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v/>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -902,47 +900,45 @@
         <v/>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>No shots made</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v/>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:15:45.529Z</t>
+          <t>2026-04-10T15:15:44.168Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5980</v>
+        <v>9208</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -957,14 +953,14 @@
         <v/>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
@@ -976,31 +972,33 @@
       <c r="M7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Great defense, great pick up, no accuracy</t>
+          <t>Auto geeked out very fast intake didn't shoot any balls something must've been wrong</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T15:25:35.652Z</t>
+          <t>2026-04-10T15:17:50.246Z</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4967</v>
+        <v>10642</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1009,26 +1007,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Tammy</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>100</v>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Trench</t>
@@ -1038,41 +1036,43 @@
         <v/>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Lobs balls back in their zone during inactive, auto track turret, supercharged, insanely good bot and driving</t>
+          <t>No shots made</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:34:05.525Z</t>
+          <t>2026-04-10T15:15:45.529Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10.csv</t>
+          <t>scouting_2026-04-10 (1).csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7221</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v/>
+        <v>5980</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
         <v/>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1105,24 +1105,22 @@
         <v/>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v/>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>No shots made. Bot may have died on field</t>
+          <t>Great defense, great pick up, no accuracy</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T15:32:52.601Z</t>
+          <t>2026-04-10T15:25:35.652Z</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1133,106 +1131,108 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6081</v>
+        <v>4967</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="G10" s="2" t="n">
         <v/>
       </c>
       <c r="H10" s="2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
         <v/>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Scored 151 by them self</t>
+          <t>Lobs balls back in their zone during inactive, auto track turret, supercharged, insanely good bot and driving</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:43:51.580Z</t>
+          <t>2026-04-10T15:34:05.525Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7289</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
+        <v>7221</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v/>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Tammy</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
         <v/>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Trench</t>
+          <t>Bump</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -1251,106 +1251,106 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Easily stuck on top of balls, shot little balls</t>
+          <t>No shots made. Bot may have died on field</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T15:43:31.149Z</t>
+          <t>2026-04-10T15:32:52.601Z</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10.csv</t>
+          <t>scouting_2026-04-10 (1).csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>8423</v>
+        <v>7221</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
         <v/>
       </c>
       <c r="H12" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v/>
       </c>
       <c r="K12" s="2" t="n">
         <v/>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Dead on field</t>
+        </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:51:40.559Z</t>
+          <t>2026-04-10T15:31:36.419Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
         <v/>
       </c>
       <c r="H13" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
         <v/>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O13" s="3" t="n">
@@ -1390,25 +1390,25 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T16:00:21.180Z</t>
+          <t>2026-04-10T15:43:24.692Z</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7809</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1419,45 +1419,43 @@
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="F14" s="2" t="n">
+        <v/>
       </c>
       <c r="G14" s="2" t="n">
         <v/>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
       </c>
       <c r="K14" s="2" t="n">
         <v/>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="N14" s="2" t="n">
+        <v/>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Scored 151 by them self</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T16:07:40.988Z</t>
+          <t>2026-04-10T15:43:51.580Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1468,10 +1466,10 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>858</v>
+        <v>7289</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -1484,7 +1482,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1495,14 +1493,14 @@
         <v/>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>80</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
@@ -1512,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
@@ -1521,12 +1519,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Cool googly eyes, fast intake can hold good amount of balls</t>
+          <t>Easily stuck on top of balls, shot little balls</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T16:17:38.376Z</t>
+          <t>2026-04-10T15:43:31.149Z</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1537,19 +1535,19 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9638</v>
+        <v>5166</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1564,63 +1562,63 @@
         <v/>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v/>
+        <v>90</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
       </c>
       <c r="K16" s="2" t="n">
         <v/>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Support bot</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v/>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T16:17:18.461Z</t>
+          <t>2026-04-10T15:51:29.539Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1023</v>
+        <v>8423</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Tammy</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1631,55 +1629,55 @@
         <v/>
       </c>
       <c r="H17" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Trench</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
         <v/>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>Auto track tureet, lobs back to their zone during inactive, gets stuck on bump</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v/>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T16:26:09.766Z</t>
+          <t>2026-04-10T15:51:40.559Z</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10.csv</t>
+          <t>scouting_2026-04-10 (1).csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7289</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v/>
+        <v>2771</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1698,36 +1696,36 @@
         <v/>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
       </c>
       <c r="K18" s="2" t="n">
         <v/>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Stuck on balls in corner</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v/>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T16:24:43.193Z</t>
+          <t>2026-04-10T16:00:21.180Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1738,19 +1736,19 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>904</v>
+        <v>10642</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -1768,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1779,94 +1777,630 @@
         <v/>
       </c>
       <c r="L19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>Couldn't get under trench, gets stuck on bump. Got trapped in the neutral zone</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v/>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T16:40:55.550Z</t>
+          <t>2026-04-10T16:00:12.609Z</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10.csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4967</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:08:14.847Z</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10I.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7809</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Tammy</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:07:40.988Z</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10 (1).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Cool googly eyes, fast intake can hold good amount of balls</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:17:38.376Z</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6081</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:17:09.770Z</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10I.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>9638</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Tammy</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Support bot</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:17:18.461Z</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10 (1).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Auto track tureet, lobs back to their zone during inactive, gets stuck on bump</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:26:09.766Z</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7289</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Tammy</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Stuck on balls in corner</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:24:43.193Z</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10 (1).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>904</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Couldn't get under trench, gets stuck on bump. Got trapped in the neutral zone</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T16:40:55.550Z</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>scouting_2026-04-10.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>7656</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tammy</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E28" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H20" s="2" t="n">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="K28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>2026-04-10T16:40:29.152Z</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>scouting_2026-04-10 (1).csv</t>
         </is>
@@ -1883,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2087,15 +2621,15 @@
         <v>1023</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -2106,10 +2640,10 @@
         <v/>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -2130,78 +2664,78 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Auto track tureet, lobs back to their zone during inactive, gets stuck on bump</t>
-        </is>
+      <c r="N4" s="2" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2771</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H5" s="3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
         <v/>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Auto track tureet, lobs back to their zone during inactive, gets stuck on bump</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4967</v>
+        <v>2771</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -2212,42 +2746,40 @@
         <v/>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Trench</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v/>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Lobs balls back in their zone during inactive, auto track turret, supercharged, insanely good bot and driving</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5980</v>
+        <v>3234</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -2266,98 +2798,102 @@
         <v/>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
         <v/>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Great defense, great pick up, no accuracy</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6081</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="F8" s="2" t="n">
         <v/>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v/>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Scored 151 by them self</t>
+          <t>Lobs balls back in their zone during inactive, auto track turret, supercharged, insanely good bot and driving</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7220</v>
+        <v>4967</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3167</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -2368,94 +2904,92 @@
         <v/>
       </c>
       <c r="G9" s="3" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Trench</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
         <v/>
       </c>
       <c r="K9" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>4</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Score for auto got stuck on . Over all good bot,</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7221</v>
+        <v>5166</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v/>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>No shots made. Bot may have died on field</t>
-        </is>
+      <c r="N10" s="2" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7256</v>
+        <v>5980</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -2467,109 +3001,105 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
         <v/>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Bump</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
         <v/>
       </c>
       <c r="K11" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v/>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Only 2 shots made</t>
+          <t>Great defense, great pick up, no accuracy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7289</v>
+        <v>6081</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v/>
       </c>
       <c r="F12" s="2" t="n">
         <v/>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Trench</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
         <v/>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v/>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Easily stuck on top of balls, shot little balls</t>
+          <t>Scored 151 by them self</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7289</v>
+        <v>6081</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -2580,10 +3110,10 @@
         <v/>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I13" s="3" t="n">
         <v/>
@@ -2595,25 +3125,23 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Stuck on balls in corner</t>
-        </is>
+      <c r="N13" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7656</v>
+        <v>7220</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -2621,7 +3149,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24</v>
+        <v>3167</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2632,10 +3160,10 @@
         <v/>
       </c>
       <c r="G14" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2656,21 +3184,21 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
-        <v/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Score for auto got stuck on . Over all good bot,</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>7809</v>
+        <v>7221</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v/>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -2684,96 +3212,98 @@
         <v/>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
       <c r="J15" s="3" t="n">
         <v/>
       </c>
       <c r="K15" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>No shots made. Bot may have died on field</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8423</v>
+        <v>7221</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v/>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
         <v/>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
-        <v/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Dead on field</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9208</v>
+        <v>7256</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -2781,49 +3311,49 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v/>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>50</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Trench</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
         <v/>
       </c>
       <c r="K17" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Auto geeked out very fast intake didn't shoot any balls something must've been wrong</t>
+          <t>Only 2 shots made</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9638</v>
+        <v>7289</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -2831,7 +3361,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -2842,48 +3372,48 @@
         <v/>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
       </c>
       <c r="J18" s="2" t="n">
         <v/>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Support bot</t>
+          <t>Easily stuck on top of balls, shot little balls</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>9756</v>
+        <v>7289</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v/>
       </c>
       <c r="D19" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -2894,88 +3424,506 @@
         <v/>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v/>
       </c>
       <c r="J19" s="3" t="n">
         <v/>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Fast lil guy</t>
+          <t>Stuck on balls in corner</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>7656</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>7658</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Stuck field fault</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>7809</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>8423</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>9208</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Auto geeked out very fast intake didn't shoot any balls something must've been wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>9638</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Support bot</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>9756</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Fast lil guy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>10642</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
+      <c r="F27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Trench</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="2" t="n">
+      <c r="J27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>No shots made</t>
         </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>10642</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Trench</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2989,7 +3937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3046,25 +3994,25 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6081</v>
+        <v>7220</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>3167</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>4</v>
@@ -3072,25 +4020,25 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>7220</v>
+        <v>6081</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3167</v>
+        <v>11.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>50</v>
+        <v>77.5</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>4</v>
@@ -3150,19 +4098,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>858</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -3171,160 +4119,160 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>5980</v>
+        <v>858</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1023</v>
+        <v>4967</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>4967</v>
+        <v>3234</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8423</v>
+        <v>5980</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="E10" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7809</v>
+        <v>8423</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9756</v>
+        <v>5166</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>4</v>
@@ -3332,7 +4280,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7256</v>
+        <v>7809</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
@@ -3344,39 +4292,39 @@
         <v>2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7289</v>
+        <v>7256</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2</v>
@@ -3384,45 +4332,45 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>904</v>
+        <v>9756</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7221</v>
+        <v>7289</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -3431,12 +4379,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>9208</v>
+        <v>904</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1</v>
@@ -3454,18 +4402,18 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9638</v>
+        <v>7221</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
@@ -3474,21 +4422,21 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>10642</v>
+        <v>7658</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>1</v>
@@ -3500,16 +4448,94 @@
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>9208</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="3" t="n">
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>9638</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>10642</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
